--- a/data/trans_dic/IP36A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que perciben algun tipo de pensión</t>
+          <t>Adultos que perciben algun tipo de pensión (tasa de respuesta: 99,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 10,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 18,12</t>
+          <t>6,1; 17,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 11,94</t>
+          <t>2,53; 11,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 26,12</t>
+          <t>2,56; 27,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,87</t>
+          <t>0,0; 8,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 14,45</t>
+          <t>4,61; 15,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,07</t>
+          <t>2,18; 12,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 35,64</t>
+          <t>6,8; 35,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,91</t>
+          <t>0,6; 6,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 14,2</t>
+          <t>6,43; 13,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,72</t>
+          <t>3,0; 9,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 25,28</t>
+          <t>7,23; 28,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 13,74</t>
+          <t>4,08; 13,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,89</t>
+          <t>4,83; 13,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,85</t>
+          <t>1,94; 8,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 24,33</t>
+          <t>8,11; 24,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,73</t>
+          <t>3,55; 11,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 15,49</t>
+          <t>6,64; 15,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 15,93</t>
+          <t>6,6; 16,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,61; 38,06</t>
+          <t>19,33; 39,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 10,52</t>
+          <t>4,67; 10,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 12,84</t>
+          <t>6,95; 12,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,43</t>
+          <t>5,43; 11,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,05; 28,79</t>
+          <t>15,55; 29,19</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 14,35</t>
+          <t>3,78; 14,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 11,64</t>
+          <t>3,21; 12,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 18,64</t>
+          <t>8,04; 18,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,72; 39,26</t>
+          <t>15,29; 38,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 13,0</t>
+          <t>2,23; 12,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 14,89</t>
+          <t>4,83; 15,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 19,85</t>
+          <t>7,93; 20,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 25,6</t>
+          <t>8,56; 25,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 11,37</t>
+          <t>4,11; 11,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,55</t>
+          <t>4,62; 11,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,49; 17,29</t>
+          <t>9,52; 16,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,6; 29,85</t>
+          <t>15,14; 30,49</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 14,64</t>
+          <t>4,68; 14,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 21,93</t>
+          <t>9,45; 22,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 15,82</t>
+          <t>5,32; 16,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 19,21</t>
+          <t>5,12; 18,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 17,3</t>
+          <t>6,2; 16,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 17,44</t>
+          <t>7,33; 17,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,31; 26,4</t>
+          <t>11,78; 26,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 23,5</t>
+          <t>10,2; 24,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 13,96</t>
+          <t>6,49; 13,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 17,22</t>
+          <t>9,43; 17,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,13; 18,84</t>
+          <t>10,11; 19,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 18,41</t>
+          <t>8,95; 18,45</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,21</t>
+          <t>5,15; 10,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,72</t>
+          <t>7,73; 12,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,0</t>
+          <t>6,17; 10,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,3; 21,24</t>
+          <t>10,27; 21,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,66</t>
+          <t>4,95; 9,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,77</t>
+          <t>7,82; 12,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 15,5</t>
+          <t>9,4; 15,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,33; 23,07</t>
+          <t>14,81; 23,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,02</t>
+          <t>5,68; 9,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,04</t>
+          <t>8,41; 11,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,64</t>
+          <t>8,7; 12,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,82</t>
+          <t>13,57; 21,07</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que perciben algun tipo de pensión (tasa de respuesta: 99,16%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9024</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6950</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3330</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2519</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15974</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7454</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5282</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4259</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5001; 14588</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1756; 7735</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>462; 5055</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4976</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3816; 12739</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1317; 7453</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1260; 6576</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>589; 6044</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10601; 22970</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3899; 12458</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2646; 10261</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8272</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10814</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4845</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7475</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7279</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15017</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13056</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>17025</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>15551</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25831</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17902</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>24500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4238; 13704</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6270; 17340</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1950; 8901</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4082; 12204</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3832; 12211</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9523; 21875</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8206; 19895</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>12010; 24605</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>9898; 21954</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>19004; 35238</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>12215; 25243</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>17495; 32842</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5776</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5186</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11985</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17156</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7374</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12661</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12560</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24646</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>27108</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2724; 10781</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2653; 10030</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7695; 17795</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10212; 25828</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1260; 6969</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3892; 12246</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7546; 19526</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5541; 16665</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5287; 15198</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7533; 18918</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18170; 32392</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>19915; 40108</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7345</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13474</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8851</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14814</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10092</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12417</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15708</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>17745</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>17437</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25891</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>24559</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>32558</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3878; 12010</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8480; 20090</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4865; 14903</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6401; 23666</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>5901; 15531</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>7784; 18932</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9914; 22665</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>11479; 27496</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11564; 24687</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>18480; 33602</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>17743; 34992</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>21261; 43836</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>22499</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>38497</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29884</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>41397</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41758</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>48051</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>44624</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>80256</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>74560</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>89448</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>15541; 30403</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>29687; 48926</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22052; 38235</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26728; 56756</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15633; 29705</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>32288; 51979</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>34212; 55659</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>38180; 61063</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>35070; 55613</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>67089; 94406</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>62753; 89150</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>70319; 109177</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP36A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,01</t>
+          <t>0,0; 9,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 17,78</t>
+          <t>6,14; 17,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 11,16</t>
+          <t>2,68; 12,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 27,97</t>
+          <t>3,56; 29,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,89</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 15,39</t>
+          <t>4,46; 15,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,32</t>
+          <t>1,97; 11,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 35,49</t>
+          <t>6,3; 34,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,13</t>
+          <t>0,69; 6,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 13,94</t>
+          <t>6,61; 14,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,6</t>
+          <t>3,18; 9,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 28,03</t>
+          <t>7,25; 26,23</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 13,18</t>
+          <t>4,3; 13,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 13,36</t>
+          <t>5,2; 13,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,84</t>
+          <t>2,26; 8,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,11; 24,24</t>
+          <t>8,06; 24,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 11,32</t>
+          <t>3,6; 11,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 15,25</t>
+          <t>6,91; 15,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 16,01</t>
+          <t>6,32; 15,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,33; 39,6</t>
+          <t>18,18; 37,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,36</t>
+          <t>4,83; 10,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 12,89</t>
+          <t>6,74; 12,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,22</t>
+          <t>5,34; 11,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,55; 29,19</t>
+          <t>15,83; 28,78</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,96</t>
+          <t>3,83; 15,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 12,14</t>
+          <t>2,99; 11,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 18,6</t>
+          <t>7,67; 18,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,29; 38,67</t>
+          <t>15,91; 39,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 12,32</t>
+          <t>2,24; 11,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 15,19</t>
+          <t>4,98; 15,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 20,53</t>
+          <t>8,19; 19,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,56; 25,75</t>
+          <t>8,43; 24,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 11,81</t>
+          <t>3,73; 11,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 11,59</t>
+          <t>4,8; 11,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,52; 16,98</t>
+          <t>9,42; 17,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,14; 30,49</t>
+          <t>14,65; 29,46</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 14,49</t>
+          <t>4,7; 14,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 22,39</t>
+          <t>9,3; 21,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 16,3</t>
+          <t>5,8; 15,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 18,92</t>
+          <t>5,19; 19,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 16,32</t>
+          <t>6,25; 15,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 17,83</t>
+          <t>7,48; 18,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,78; 26,94</t>
+          <t>12,3; 26,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 24,44</t>
+          <t>10,02; 23,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 13,86</t>
+          <t>6,89; 13,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 17,15</t>
+          <t>9,75; 18,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 19,93</t>
+          <t>10,0; 19,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 18,45</t>
+          <t>8,53; 19,01</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,08</t>
+          <t>5,25; 10,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,73</t>
+          <t>7,8; 12,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,71</t>
+          <t>6,29; 10,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,27; 21,81</t>
+          <t>10,79; 21,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,41</t>
+          <t>5,03; 9,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,58</t>
+          <t>7,79; 12,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 15,29</t>
+          <t>9,62; 15,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,81; 23,68</t>
+          <t>14,67; 23,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,01</t>
+          <t>5,78; 9,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 11,84</t>
+          <t>8,36; 11,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,36</t>
+          <t>8,53; 12,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,57; 21,07</t>
+          <t>13,56; 20,74</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4259</t>
+          <t>0; 3966</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5001; 14588</t>
+          <t>5040; 14072</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1756; 7735</t>
+          <t>1860; 8412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>462; 5055</t>
+          <t>643; 5248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4976</t>
+          <t>0; 4348</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3816; 12739</t>
+          <t>3695; 12528</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1317; 7453</t>
+          <t>1191; 7228</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1260; 6576</t>
+          <t>1167; 6334</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>589; 6044</t>
+          <t>677; 6580</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10601; 22970</t>
+          <t>10899; 23263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3899; 12458</t>
+          <t>4123; 12583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2646; 10261</t>
+          <t>2655; 9601</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4238; 13704</t>
+          <t>4469; 13902</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6270; 17340</t>
+          <t>6746; 18036</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1950; 8901</t>
+          <t>2277; 9038</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4082; 12204</t>
+          <t>4057; 12325</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3832; 12211</t>
+          <t>3886; 12372</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9523; 21875</t>
+          <t>9914; 21541</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8206; 19895</t>
+          <t>7847; 18909</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12010; 24605</t>
+          <t>11294; 23385</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9898; 21954</t>
+          <t>10239; 22396</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19004; 35238</t>
+          <t>18408; 34437</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12215; 25243</t>
+          <t>12010; 25211</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17495; 32842</t>
+          <t>17802; 32370</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2724; 10781</t>
+          <t>2758; 10836</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2653; 10030</t>
+          <t>2470; 9898</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7695; 17795</t>
+          <t>7338; 17927</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10212; 25828</t>
+          <t>10627; 26230</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1260; 6969</t>
+          <t>1265; 6738</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3892; 12246</t>
+          <t>4016; 12094</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7546; 19526</t>
+          <t>7791; 18981</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5541; 16665</t>
+          <t>5459; 15723</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5287; 15198</t>
+          <t>4795; 14420</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7533; 18918</t>
+          <t>7841; 18632</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18170; 32392</t>
+          <t>17976; 33665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19915; 40108</t>
+          <t>19269; 38748</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3878; 12010</t>
+          <t>3893; 12175</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8480; 20090</t>
+          <t>8348; 19527</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4865; 14903</t>
+          <t>5301; 14591</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6401; 23666</t>
+          <t>6492; 23852</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5901; 15531</t>
+          <t>5947; 15120</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7784; 18932</t>
+          <t>7942; 19358</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9914; 22665</t>
+          <t>10349; 22636</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11479; 27496</t>
+          <t>11270; 26047</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11564; 24687</t>
+          <t>12266; 24270</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18480; 33602</t>
+          <t>19109; 35458</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17743; 34992</t>
+          <t>17547; 33450</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21261; 43836</t>
+          <t>20273; 45168</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15541; 30403</t>
+          <t>15827; 30572</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29687; 48926</t>
+          <t>29964; 48322</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22052; 38235</t>
+          <t>22450; 38589</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26728; 56756</t>
+          <t>28086; 55108</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15633; 29705</t>
+          <t>15861; 30825</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32288; 51979</t>
+          <t>32162; 53201</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34212; 55659</t>
+          <t>35004; 55841</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38180; 61063</t>
+          <t>37838; 60364</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35070; 55613</t>
+          <t>35680; 55861</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67089; 94406</t>
+          <t>66616; 95421</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62753; 89150</t>
+          <t>61533; 89457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70319; 109177</t>
+          <t>70261; 107481</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP36A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP36A-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,32</t>
+          <t>0,0; 8,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 17,15</t>
+          <t>4,22; 14,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 12,14</t>
+          <t>2,02; 11,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 29,04</t>
+          <t>6,99; 39,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 15,13</t>
+          <t>6,49; 18,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,94</t>
+          <t>2,55; 11,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 34,18</t>
+          <t>2,43; 28,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,68</t>
+          <t>0,73; 6,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 14,11</t>
+          <t>6,47; 14,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,69</t>
+          <t>3,22; 9,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 26,23</t>
+          <t>8,01; 27,7</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,95%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,33%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,81%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 13,37</t>
+          <t>3,2; 11,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 13,89</t>
+          <t>7,09; 15,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,97</t>
+          <t>6,68; 15,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 24,48</t>
+          <t>18,71; 39,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 11,47</t>
+          <t>4,39; 13,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 15,01</t>
+          <t>4,95; 12,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 15,22</t>
+          <t>2,2; 8,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 37,64</t>
+          <t>8,18; 24,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,57</t>
+          <t>4,79; 10,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 12,6</t>
+          <t>6,59; 12,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 11,21</t>
+          <t>5,5; 11,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,83; 28,78</t>
+          <t>15,98; 29,4</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,31%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16,06%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8,01%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>12,53%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>25,68%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 15,03</t>
+          <t>2,23; 13,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 11,98</t>
+          <t>4,75; 14,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 18,74</t>
+          <t>8,27; 19,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,91; 39,27</t>
+          <t>8,83; 26,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 11,91</t>
+          <t>3,92; 14,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 15,0</t>
+          <t>3,07; 11,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,19; 19,96</t>
+          <t>8,08; 18,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 24,29</t>
+          <t>15,32; 34,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 11,21</t>
+          <t>3,83; 11,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,42</t>
+          <t>4,88; 11,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,42; 17,65</t>
+          <t>9,49; 17,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,65; 29,46</t>
+          <t>14,62; 28,2</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,67%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16,61%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,86%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15,01%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 14,69</t>
+          <t>6,52; 17,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 21,76</t>
+          <t>7,61; 17,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 15,96</t>
+          <t>12,31; 26,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 19,07</t>
+          <t>10,41; 24,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 15,89</t>
+          <t>4,75; 14,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 18,23</t>
+          <t>9,4; 21,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 26,9</t>
+          <t>5,28; 15,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 23,15</t>
+          <t>10,03; 24,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,63</t>
+          <t>6,75; 13,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 18,1</t>
+          <t>9,35; 17,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 19,05</t>
+          <t>10,13; 18,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 19,01</t>
+          <t>11,95; 21,94</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,14</t>
+          <t>5,17; 9,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,58</t>
+          <t>7,96; 12,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 10,81</t>
+          <t>9,59; 15,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,79; 21,17</t>
+          <t>14,87; 23,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,77</t>
+          <t>5,2; 10,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,88</t>
+          <t>7,89; 12,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 15,34</t>
+          <t>6,21; 11,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,67; 23,41</t>
+          <t>13,38; 22,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,05</t>
+          <t>5,78; 9,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 11,97</t>
+          <t>8,41; 12,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,41</t>
+          <t>8,78; 12,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,56; 20,74</t>
+          <t>15,45; 21,98</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1514,37 +1514,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6950</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3033</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1107</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9024</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4203</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6950</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>4758</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3966</t>
+          <t>0; 4965</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5040; 14072</t>
+          <t>3496; 11962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1860; 8412</t>
+          <t>1220; 6697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>643; 5248</t>
+          <t>1055; 5974</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4348</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3695; 12528</t>
+          <t>5327; 14862</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1191; 7228</t>
+          <t>1771; 8272</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1167; 6334</t>
+          <t>383; 4442</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>677; 6580</t>
+          <t>719; 6809</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10899; 23263</t>
+          <t>10665; 23404</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4123; 12583</t>
+          <t>4183; 12624</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2655; 9601</t>
+          <t>2472; 8551</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7279</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15017</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13056</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14755</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8272</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10814</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4845</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7475</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7279</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15017</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13056</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24500</t>
+          <t>21598</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4469; 13902</t>
+          <t>3455; 12656</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6746; 18036</t>
+          <t>10177; 22227</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2277; 9038</t>
+          <t>8306; 19787</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4057; 12325</t>
+          <t>9862; 20587</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3886; 12372</t>
+          <t>4563; 14289</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9914; 21541</t>
+          <t>6425; 16732</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7847; 18909</t>
+          <t>2213; 8913</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11294; 23385</t>
+          <t>3742; 11141</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10239; 22396</t>
+          <t>10154; 22291</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18408; 34437</t>
+          <t>18022; 35104</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12010; 25211</t>
+          <t>12377; 25705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17802; 32370</t>
+          <t>15731; 28947</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7374</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12661</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9961</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5776</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5186</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>11985</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17156</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3341</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7374</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12661</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27108</t>
+          <t>25448</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2758; 10836</t>
+          <t>1264; 7354</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2470; 9898</t>
+          <t>3830; 12005</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7338; 17927</t>
+          <t>7868; 18879</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10627; 26230</t>
+          <t>5478; 16558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1265; 6738</t>
+          <t>2829; 10344</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4016; 12094</t>
+          <t>2538; 9611</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7791; 18981</t>
+          <t>7729; 17828</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5459; 15723</t>
+          <t>9879; 22387</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4795; 14420</t>
+          <t>4923; 14626</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7841; 18632</t>
+          <t>7972; 18847</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17976; 33665</t>
+          <t>18111; 32981</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19269; 38748</t>
+          <t>18496; 35668</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10092</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12417</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15708</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17682</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7345</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>13474</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8851</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14814</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10092</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12417</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15708</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17745</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32558</t>
+          <t>33563</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3893; 12175</t>
+          <t>6202; 16468</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8348; 19527</t>
+          <t>8085; 18526</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5301; 14591</t>
+          <t>10353; 22210</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6492; 23852</t>
+          <t>11083; 25785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5947; 15120</t>
+          <t>3940; 12133</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7942; 19358</t>
+          <t>8436; 19681</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10349; 22636</t>
+          <t>4823; 14465</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11270; 26047</t>
+          <t>10018; 24067</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12266; 24270</t>
+          <t>12014; 24860</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19109; 35458</t>
+          <t>18322; 33734</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17547; 33450</t>
+          <t>17784; 33070</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20273; 45168</t>
+          <t>24658; 45268</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>41758</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>45431</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>22499</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>38497</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>29884</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>41397</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22125</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>41758</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44676</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>85368</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15827; 30572</t>
+          <t>16332; 30481</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29964; 48322</t>
+          <t>32893; 52758</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22450; 38589</t>
+          <t>34909; 56409</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28086; 55108</t>
+          <t>35136; 56314</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15861; 30825</t>
+          <t>15685; 30786</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32162; 53201</t>
+          <t>30332; 48868</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35004; 55841</t>
+          <t>22178; 39283</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37838; 60364</t>
+          <t>30227; 51476</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35680; 55861</t>
+          <t>35697; 55657</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66616; 95421</t>
+          <t>67069; 96012</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61533; 89457</t>
+          <t>63317; 91117</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70261; 107481</t>
+          <t>71378; 101591</t>
         </is>
       </c>
     </row>
